--- a/www/download/IND.value.m.mv.EXI382.xlsx
+++ b/www/download/IND.value.m.mv.EXI382.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,144 +688,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13.969</t>
+          <t>15485278.2377639</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.621</t>
+          <t>8194295.41191192</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6.239</t>
+          <t>6692849.55933642</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7.803</t>
+          <t>8408384.32010137</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7.462</t>
+          <t>8122275.59225796</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.532</t>
+          <t>7196493.53776237</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.617</t>
+          <t>7313235.0478051</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.943</t>
+          <t>7731411.48180802</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>6.874</t>
+          <t>7481103.76899376</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6.281</t>
+          <t>6995754.86063787</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>5.925</t>
+          <t>6613472.11574807</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>5.454</t>
+          <t>6035181.15127631</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>4.373</t>
+          <t>4795387.63615969</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>4.918</t>
+          <t>5427736.0027874</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5907534.99041684</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>3.782</t>
+          <t>4128499.8076394</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>3.662</t>
+          <t>4044001.52477413</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3.134</t>
+          <t>3444611.30996743</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3684041.33416152</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3.715</t>
+          <t>4101495.55510177</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.855</t>
+          <t>3077090.58070199</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2.699</t>
+          <t>2883245.62184296</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2.795</t>
+          <t>2956657.31048871</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.037</t>
+          <t>3217680.55917382</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.808</t>
+          <t>2955633.67089472</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2.838</t>
+          <t>3036193.51867595</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2.788</t>
+          <t>2982262.6596701</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,144 +835,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7.624</t>
+          <t>6766343.92269162</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>6121786.35239903</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6.937</t>
+          <t>5819065.18337622</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7.139</t>
+          <t>6014393.14206309</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7.134</t>
+          <t>6077950.02417771</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.635</t>
+          <t>5647185.322014</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6.885</t>
+          <t>5934896.85470918</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>5466533.21584615</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>6.271</t>
+          <t>5362317.20646748</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6.233</t>
+          <t>5324948.13458416</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>5.829</t>
+          <t>5001207.46765156</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5.158</t>
+          <t>4421966.53071547</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>4.868</t>
+          <t>4138275.54758323</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4042374.40626261</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4168860.67183021</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>4.664</t>
+          <t>4035273.2013378</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>4.377</t>
+          <t>3850808.96318453</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>4.729</t>
+          <t>4111525.12813902</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>4.716</t>
+          <t>4109764.53428274</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>3375676.09016478</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3.395</t>
+          <t>2921267.66612004</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3.307</t>
+          <t>2852772.76152629</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2.949</t>
+          <t>2522507.45830726</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.167</t>
+          <t>2731074.96067939</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.211</t>
+          <t>2762671.55537505</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>3.223</t>
+          <t>2790709.17854698</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>3.323</t>
+          <t>2881219.61528227</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,144 +982,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>33.154</t>
+          <t>27624822.8429843</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>156.891</t>
+          <t>120865253.11514</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6.933</t>
+          <t>6198535.85846957</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6.815</t>
+          <t>6136806.98537602</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>106.282</t>
+          <t>82224134.5718697</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.456</t>
+          <t>5815705.034201</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6.892</t>
+          <t>6233027.88908832</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20.448</t>
+          <t>16488965.9482111</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6.743</t>
+          <t>6032299.78902046</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>7.076</t>
+          <t>6419970.85443853</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6.709</t>
+          <t>6110679.55868462</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>25.888</t>
+          <t>20643524.843358</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4761316.15577679</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6.408</t>
+          <t>5705602.83583409</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>5.551</t>
+          <t>5057841.87002925</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>5.024</t>
+          <t>4525309.72683836</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>4651188.14051406</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>5.135</t>
+          <t>4650558.90710789</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>5.847</t>
+          <t>5329946.28788175</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>4.966</t>
+          <t>4534192.38201831</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4.559</t>
+          <t>4165747.09020519</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>94.898</t>
+          <t>73269431.9076962</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>4.893</t>
+          <t>4311121.92925311</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.552</t>
+          <t>4110285.05677634</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.036</t>
+          <t>3639796.52127792</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>4.316</t>
+          <t>3900864.93694594</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>4.373</t>
+          <t>4022288.96310469</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,144 +1129,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>91.261</t>
+          <t>75697649.6892674</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>144.787</t>
+          <t>121165127.176041</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>88.646</t>
+          <t>74820095.792027</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.906</t>
+          <t>55119292.5111839</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>63.477</t>
+          <t>53489859.6714749</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>53.989</t>
+          <t>45542775.6876039</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>42.152</t>
+          <t>35903207.4902502</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>37.531</t>
+          <t>31482885.0614879</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>34.734</t>
+          <t>29220597.2148452</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>34.727</t>
+          <t>29892209.2453798</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>28.357</t>
+          <t>24297803.4747005</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>26.266</t>
+          <t>22431126.5540919</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>20.332</t>
+          <t>17493498.2042581</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>23.701</t>
+          <t>20244781.6677139</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>18.768</t>
+          <t>16192186.0610757</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>17.268</t>
+          <t>14904612.6948075</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>16.334</t>
+          <t>14043727.1985245</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>14.294</t>
+          <t>12378251.8097153</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>13.526</t>
+          <t>11709184.451043</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>16.907</t>
+          <t>14598213.5323324</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>24.775</t>
+          <t>20531800.8297237</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>16.068</t>
+          <t>13798660.2910909</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>20.689</t>
+          <t>17239068.915723</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.322</t>
+          <t>12972197.6469019</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>15.989</t>
+          <t>13501357.3155634</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18.654</t>
+          <t>15653051.7002822</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>16.409</t>
+          <t>13654978.2866094</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1271,144 +1276,144 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>61.078</t>
+          <t>46455657.5084267</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>32.066</t>
+          <t>24092870.4562068</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26.582</t>
+          <t>20081379.9889769</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>26.708</t>
+          <t>20165789.6345964</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>33.051</t>
+          <t>24946658.4005196</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28.272</t>
+          <t>21390420.8000452</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>27.908</t>
+          <t>21145189.4766447</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32.321</t>
+          <t>24459942.9786967</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>32.836</t>
+          <t>24886899.1657861</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30.118</t>
+          <t>22837896.7854027</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>27.205</t>
+          <t>20624760.7079258</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>24.286</t>
+          <t>18417286.6604647</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>20.111</t>
+          <t>15254160.1641056</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>18.306</t>
+          <t>13942120.3587773</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>16.768</t>
+          <t>12756885.4489713</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>14.704</t>
+          <t>11203195.2762362</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>11.186</t>
+          <t>8584937.68074383</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>8082105.10902374</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>10.886</t>
+          <t>8359703.40067512</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>18.289</t>
+          <t>13894511.1393357</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>19.542</t>
+          <t>14801989.4085058</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>13050400.204693</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>18.577</t>
+          <t>14084102.9391831</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.843</t>
+          <t>15027370.4830724</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>17.855</t>
+          <t>13544976.1918576</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17.083</t>
+          <t>12972182.1057405</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>17.035</t>
+          <t>12938269.4846626</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,144 +1423,144 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21.446</t>
+          <t>17518811.5353042</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6.194</t>
+          <t>5099220.74615977</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6.669</t>
+          <t>5426400.9795316</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5.715</t>
+          <t>4722175.70295634</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.202</t>
+          <t>4331141.68470213</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.337</t>
+          <t>4478863.02636054</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.116</t>
+          <t>3493790.63348464</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.982</t>
+          <t>4279002.20583518</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4.644</t>
+          <t>3923876.45196119</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4.851</t>
+          <t>4122753.28069388</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>4.629</t>
+          <t>3918815.69790213</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4.648</t>
+          <t>3898636.51942733</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>3.598</t>
+          <t>3024624.02055366</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3.787</t>
+          <t>3244786.62820269</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>4.202</t>
+          <t>3638515.82494136</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>3.414</t>
+          <t>3019469.43141418</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>3.389</t>
+          <t>3037001.76882673</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3036127.06041043</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>3.157</t>
+          <t>2772933.43305749</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>4.366</t>
+          <t>3707408.01642715</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4073261.08475371</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3202942.0213392</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>3.835</t>
+          <t>3144154.59155431</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.929</t>
+          <t>3242640.60112117</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.534</t>
+          <t>2912248.64499961</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>3.717</t>
+          <t>3060480.52014032</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>2958379.39043086</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,144 +1570,144 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3598.582</t>
+          <t>2761388781.94337</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>210.258</t>
+          <t>140495326.514235</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>207.085</t>
+          <t>142176403.919333</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>140.091</t>
+          <t>96034271.6502948</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>112.569</t>
+          <t>77302354.335201</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>91.658</t>
+          <t>63351635.3675686</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>87.648</t>
+          <t>60594502.854469</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>86.686</t>
+          <t>59721653.6722051</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>119.325</t>
+          <t>82118981.910322</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>94.609</t>
+          <t>65184652.0325339</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>128.107</t>
+          <t>88661974.4334624</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>84.341</t>
+          <t>57896113.7455265</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>48805858.4751934</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>59.425</t>
+          <t>40991895.6419429</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>48.095</t>
+          <t>33322170.5663072</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>37.574</t>
+          <t>26001839.8386411</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>34.145</t>
+          <t>23699883.1691996</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>27.403</t>
+          <t>19104286.9246863</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>26.798</t>
+          <t>18614641.2094337</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>61.734</t>
+          <t>43692076.5214504</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>53.676</t>
+          <t>38029389.6143712</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>62.215</t>
+          <t>44179470.8698168</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>55.695</t>
+          <t>39448152.384626</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>53.032</t>
+          <t>37670890.9934644</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>53.533</t>
+          <t>37936047.8839712</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>51.542</t>
+          <t>36560735.3930219</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>51.162</t>
+          <t>36339211.7492255</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1712,144 +1717,144 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>44.167</t>
+          <t>36848936.1433097</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13896.842</t>
+          <t>10946436752.9359</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>12306930.734941</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>11.874</t>
+          <t>10760225.1530261</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>11.191</t>
+          <t>10194337.0149892</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>10817745.0051483</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17.375</t>
+          <t>15478765.4006008</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.875</t>
+          <t>12629494.3845492</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>13.267</t>
+          <t>11819704.3704056</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>11.828</t>
+          <t>10765947.9068601</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>8.985</t>
+          <t>8379158.93297928</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>552.456</t>
+          <t>436088334.694228</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>7.071</t>
+          <t>6395515.01765503</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>597.337</t>
+          <t>471467062.862278</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>7.366</t>
+          <t>6747046.88551398</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>7.376</t>
+          <t>6689968.76602279</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>7.826</t>
+          <t>7230583.48361542</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>8.953</t>
+          <t>7976987.42488029</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>6.735</t>
+          <t>6220474.81748632</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>11562.325</t>
+          <t>9107146085.84462</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>7453.299</t>
+          <t>5870794404.01711</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>50280.459</t>
+          <t>39600954045.0053</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>7634.517</t>
+          <t>6013427067.50947</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.238</t>
+          <t>5608483.41424682</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4457023.62994064</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>5.752</t>
+          <t>5201842.64502584</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5.902</t>
+          <t>5121225.51885597</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1859,144 +1864,144 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>70.253</t>
+          <t>66520665.1709219</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20.117</t>
+          <t>20347781.6911803</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19.695</t>
+          <t>19972848.9772322</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>17545855.3581079</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.436</t>
+          <t>17773143.0220776</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>14.857</t>
+          <t>15373074.3368307</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13.975</t>
+          <t>14383728.1335876</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12.839</t>
+          <t>13427083.1433354</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>12.167</t>
+          <t>12687109.5488662</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>10.809</t>
+          <t>11206984.6090954</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>9.838</t>
+          <t>10221756.6816042</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>9.284</t>
+          <t>9777570.85873019</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>7.611</t>
+          <t>7947936.91168166</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7300973.22068225</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>8.035</t>
+          <t>8359747.02570845</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>7.231</t>
+          <t>7656075.39108601</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>6.652</t>
+          <t>7015575.46003894</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>6.814</t>
+          <t>7215572.91318761</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>6.845</t>
+          <t>7182434.42863014</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8690186.25737438</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>10.544</t>
+          <t>10353955.3861315</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>7.038</t>
+          <t>7317940.11147282</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>65.091</t>
+          <t>58268095.5511986</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8.828</t>
+          <t>8811911.3471347</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>7.943</t>
+          <t>7916740.51394275</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>8.128</t>
+          <t>8172260.25004845</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>10.263</t>
+          <t>10014369.7772623</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,144 +2011,144 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9.838</t>
+          <t>10798891.9572277</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.126</t>
+          <t>6458334.5889173</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.586</t>
+          <t>5802519.42973616</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>5.522</t>
+          <t>5768674.92699723</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.806</t>
+          <t>6148857.55913144</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.336</t>
+          <t>5646654.27524849</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.877</t>
+          <t>5173591.85920142</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>5144253.81201893</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4.972</t>
+          <t>5294782.16410054</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5.645</t>
+          <t>6121296.23337906</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5.482</t>
+          <t>5889899.2718598</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4.628</t>
+          <t>4988236.25097148</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>4.427</t>
+          <t>4737799.25497074</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>4.361</t>
+          <t>4645014.02825064</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4.752</t>
+          <t>5054645.56320188</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>4.448</t>
+          <t>4811353.82449396</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>4.256</t>
+          <t>4614483.64743894</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3.725</t>
+          <t>4005856.12608867</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>4.176</t>
+          <t>4527401.438352</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>91.413</t>
+          <t>81551883.5352754</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>18.314</t>
+          <t>17042397.1624271</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>41.941</t>
+          <t>37901767.3052288</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>26.013</t>
+          <t>23428570.347597</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.911</t>
+          <t>4013910.48043949</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>7.087</t>
+          <t>6775830.96326244</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>29.648</t>
+          <t>26676532.3676773</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>4.401</t>
+          <t>4490783.6341048</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,144 +2158,144 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5342.036</t>
+          <t>4767022507.27923</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.131</t>
+          <t>7512013.8898281</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.785</t>
+          <t>7994373.32887386</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2681.19</t>
+          <t>2392498790.91566</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.774</t>
+          <t>5905750.88146707</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7.523</t>
+          <t>7585459.09130902</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>367.518</t>
+          <t>328591993.456279</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5.163</t>
+          <t>5418660.36271002</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6.054</t>
+          <t>6195037.96540457</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25.239</t>
+          <t>23251838.3077343</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>435.885</t>
+          <t>389596806.228811</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4411401.90804211</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>4.073</t>
+          <t>4250549.63571471</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>364.461</t>
+          <t>325823444.544069</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>8.524</t>
+          <t>8321024.15372588</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>3.498</t>
+          <t>3744690.04788786</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>3.937</t>
+          <t>4256353.90433584</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>4.147</t>
+          <t>4463785.41152209</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>4382866.06811586</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>22.613</t>
+          <t>20898210.5796315</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>26.062</t>
+          <t>23906713.3537579</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>22.702</t>
+          <t>20846018.791584</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>468460.147</t>
+          <t>417857957353.651</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15.325</t>
+          <t>14090416.2905815</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>20.602</t>
+          <t>18778589.9711683</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16.801</t>
+          <t>15386100.8449739</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>16.862</t>
+          <t>15473801.5274917</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2300,144 +2305,144 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>38.743</t>
+          <t>41505065.1221009</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9.108</t>
+          <t>10450800.6203225</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9.109</t>
+          <t>10337443.1495027</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>8.926</t>
+          <t>10226013.2203518</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8.711</t>
+          <t>10067475.9373272</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8.647</t>
+          <t>10056710.6299108</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7.632</t>
+          <t>8944597.99258576</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8.159</t>
+          <t>9524293.64738611</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6.975</t>
+          <t>8066426.80477837</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>7.407</t>
+          <t>8714056.28429341</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>6.964</t>
+          <t>8277606.74205352</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>6.927</t>
+          <t>8242377.60327241</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>5.889</t>
+          <t>6904686.63317012</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>6.521</t>
+          <t>7724611.03983004</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>6.612</t>
+          <t>7668255.19885205</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>6.103</t>
+          <t>7225538.7464851</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>7012198.81801245</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>5.888</t>
+          <t>7013308.52784933</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>5.612</t>
+          <t>6725402.48021385</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>5.547</t>
+          <t>6556739.92278918</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>4.801</t>
+          <t>5636993.19846179</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>5.004</t>
+          <t>5822955.16490417</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>5.677</t>
+          <t>6357920.13198619</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.028</t>
+          <t>5816847.83485866</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>4.849</t>
+          <t>5587866.72845368</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>4.736</t>
+          <t>5516744.98374091</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>5.348</t>
+          <t>6218520.95439544</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2447,144 +2452,144 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>68.51</t>
+          <t>74074838.2079192</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.681</t>
+          <t>49341045.4889407</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>31.353</t>
+          <t>34430881.0338309</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>34.935</t>
+          <t>37706185.1241515</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>30.397</t>
+          <t>33501699.6716116</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>38.622</t>
+          <t>44002858.2994542</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>26.955</t>
+          <t>30161196.5477063</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>23.964</t>
+          <t>26492639.5002055</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>44.102</t>
+          <t>43949950.2058042</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>64.807</t>
+          <t>62149363.9738077</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>15.291</t>
+          <t>17124874.3468131</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>18.663</t>
+          <t>20121705.4474471</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>110.76</t>
+          <t>101016186.961048</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>13084678.670302</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>11.294</t>
+          <t>12442142.8294664</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>14.441</t>
+          <t>15961631.5767153</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>8.677</t>
+          <t>9718679.27537175</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8628420.74073616</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>8976284.83479966</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>163.33</t>
+          <t>147592160.538528</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>170.734</t>
+          <t>154191169.93625</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>113.249</t>
+          <t>102774753.912019</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>108.289</t>
+          <t>98049130.7963428</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>140.889</t>
+          <t>127347030.350976</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>146.416</t>
+          <t>132311532.615817</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>149.271</t>
+          <t>134687492.06293</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>8.808</t>
+          <t>9621941.5849223</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2594,144 +2599,144 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19.526</t>
+          <t>32462211.1440931</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.143</t>
+          <t>10129476.0635436</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6.578</t>
+          <t>9335401.4621034</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7.157</t>
+          <t>9985601.01777037</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6.813</t>
+          <t>9795000.18581242</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.807</t>
+          <t>8521348.2677793</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5.835</t>
+          <t>8418635.61447228</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>5.678</t>
+          <t>8220244.20701922</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4.832</t>
+          <t>7093103.57223926</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5.142</t>
+          <t>7703969.3716791</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>7357469.82874275</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>4.102</t>
+          <t>6017597.5610881</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>4.113</t>
+          <t>6009333.50224019</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>6482604.62912758</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4.114</t>
+          <t>5794622.41891125</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>4954990.1015523</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>3.581</t>
+          <t>5204115.52795763</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>4794182.98592432</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>3.851</t>
+          <t>5481729.45142686</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>221850.427</t>
+          <t>240202964809.961</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>219005.141</t>
+          <t>237122152572.642</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>221114.243</t>
+          <t>239405795219.985</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>228920.566</t>
+          <t>247857679557.374</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>234924.801</t>
+          <t>254358562291.006</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>234421.364</t>
+          <t>253813402613.331</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>236670.477</t>
+          <t>256248578786.911</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>236645.988</t>
+          <t>256222099916.446</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,144 +2746,144 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>12.302</t>
+          <t>17508212.5721875</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6.825</t>
+          <t>9580468.03154238</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6.615</t>
+          <t>6265929.93275327</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6.246</t>
+          <t>8675323.26565333</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>7.526</t>
+          <t>10858209.2085262</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6.753</t>
+          <t>9522711.47403703</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6.357</t>
+          <t>9052238.47317852</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4.821</t>
+          <t>6542074.03004283</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4.749</t>
+          <t>5991021.27175345</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>4.916</t>
+          <t>6931568.43406383</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>5.356</t>
+          <t>7359652.46819755</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>4.168</t>
+          <t>8052610.56807142</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>3.811</t>
+          <t>8366221.57840529</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>4.477</t>
+          <t>943719.864807828</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>4.054</t>
+          <t>6503711.87516194</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>3.686</t>
+          <t>5715178.79765319</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>3.777</t>
+          <t>6071907.63449647</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>3.352</t>
+          <t>4954548.30710228</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>3.569</t>
+          <t>5789502.38240231</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2.892</t>
+          <t>4244259.45141392</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2.422</t>
+          <t>3567346.99691467</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2.814</t>
+          <t>4434536.57318848</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2.483</t>
+          <t>3552422.01363676</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.354</t>
+          <t>3387950.27956539</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.202</t>
+          <t>3145589.34087729</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2.508</t>
+          <t>3579313.72072321</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2.565</t>
+          <t>3867919.95236192</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,144 +2893,144 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>32.429</t>
+          <t>25682264.6376521</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>26.733</t>
+          <t>20729971.6844633</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>16973577.1620957</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20.519</t>
+          <t>15984225.355483</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>19.414</t>
+          <t>15194793.2789023</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>17.162</t>
+          <t>13632735.8723146</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11.285</t>
+          <t>9012519.37339061</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17.941</t>
+          <t>14004472.6567666</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>11.063</t>
+          <t>8761990.82705406</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>6.075</t>
+          <t>5102640.25885415</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>5.611</t>
+          <t>4672966.0570908</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>4201468.76303361</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>4.538</t>
+          <t>3719298.63136811</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>5.623</t>
+          <t>4630743.77978502</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>7.998</t>
+          <t>6376582.56468257</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8273354.75092087</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>10.389</t>
+          <t>8186516.22048013</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>9.932</t>
+          <t>7850852.73559484</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>9.967</t>
+          <t>7849030.20523284</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>11.168</t>
+          <t>8713176.87053667</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>11.655</t>
+          <t>8895765.6946221</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>11.996</t>
+          <t>9252167.93085556</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>11.068</t>
+          <t>8521635.5893995</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.414</t>
+          <t>7997281.09709469</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>10.464</t>
+          <t>8021582.98660348</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10.404</t>
+          <t>7980977.21774866</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>10.636</t>
+          <t>8173760.55801963</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3035,144 +3040,144 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19.976</t>
+          <t>27115555.2827904</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20.769</t>
+          <t>28953466.9926386</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>55.544</t>
+          <t>66488116.706645</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>16.484</t>
+          <t>22809897.0690464</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>15.342</t>
+          <t>21959630.5966115</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>13.555</t>
+          <t>19114537.1843149</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11.753</t>
+          <t>16560753.8169837</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>12.638</t>
+          <t>17814351.7449357</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>11.036</t>
+          <t>16016497.3634785</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>10.324</t>
+          <t>14607087.3276652</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9.729</t>
+          <t>13846583.2422782</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9.643</t>
+          <t>13298334.4620025</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>7.966</t>
+          <t>11095263.7821576</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>8.391</t>
+          <t>11646003.173325</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1584.761</t>
+          <t>1771599499.92593</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>7.568</t>
+          <t>10225456.7752108</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>8.056</t>
+          <t>10829974.0482468</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>6.216</t>
+          <t>8560121.25993185</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>6.125</t>
+          <t>8500745.81243964</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>6.328</t>
+          <t>8515104.07321786</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>7.251</t>
+          <t>9413125.62435327</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>5.622</t>
+          <t>7561905.32098813</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>6.289</t>
+          <t>8122454.61554046</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.715</t>
+          <t>7590199.2268097</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>5.643</t>
+          <t>7491503.70396729</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>5.613</t>
+          <t>7467459.05738066</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>5.129</t>
+          <t>6801132.60998191</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,144 +3187,144 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>48974535.8036535</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>31.254</t>
+          <t>41194172.0647119</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25.654</t>
+          <t>32659858.2961127</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25.552</t>
+          <t>32172497.3420514</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>25.061</t>
+          <t>32328746.4925315</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>21.845</t>
+          <t>27441431.7223058</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20.659</t>
+          <t>26062511.7088758</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>15.687</t>
+          <t>19970235.8895007</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>17.601</t>
+          <t>22093378.4403832</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>15.98</t>
+          <t>20428857.9851993</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>12.899</t>
+          <t>16845194.4715057</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>16458115.1783814</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>10.262</t>
+          <t>12834576.8610696</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>10.586</t>
+          <t>13357399.0867363</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>11.146</t>
+          <t>14036004.2604374</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>8.764</t>
+          <t>11157245.0292318</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>10.467</t>
+          <t>12742860.6725162</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>10.728</t>
+          <t>13072103.0332472</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>8.574</t>
+          <t>10738328.9201497</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2102.942</t>
+          <t>2225506149.68159</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2040.993</t>
+          <t>2159912928.67962</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2121.741</t>
+          <t>2245454485.13835</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2029.392</t>
+          <t>2147782463.76832</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>7.199</t>
+          <t>9082117.14880661</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>6.911</t>
+          <t>8639825.83599429</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>7.099</t>
+          <t>8984771.39911832</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>6.823</t>
+          <t>8657685.60302599</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,144 +3334,144 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1282.517</t>
+          <t>961044765.25144</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>266.032</t>
+          <t>199293404.665461</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>244.009</t>
+          <t>182798508.9904</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>205.857</t>
+          <t>154286575.064306</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>198.481</t>
+          <t>148849219.54679</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>177.458</t>
+          <t>133148731.181969</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>190.035</t>
+          <t>142504661.039062</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>182.24</t>
+          <t>136670153.01638</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>196.995</t>
+          <t>147714221.755609</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>171.062</t>
+          <t>128277611.297083</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>161.531</t>
+          <t>121273365.495943</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>137.693</t>
+          <t>103345690.614374</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>121.628</t>
+          <t>91310522.838214</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>125.855</t>
+          <t>94517575.0305034</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>112.975</t>
+          <t>84850714.1672968</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>84.435</t>
+          <t>63429779.0635158</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>78.53</t>
+          <t>59062842.1546688</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>55192736.6499202</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>74.993</t>
+          <t>56429876.1620894</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>154.827</t>
+          <t>116612236.579687</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>148.727</t>
+          <t>112031437.53992</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>145.188</t>
+          <t>109265315.903847</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>138.766</t>
+          <t>104435291.039546</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>174.466</t>
+          <t>131322950.394939</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>146.713</t>
+          <t>110416351.385834</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>153.231</t>
+          <t>115334348.590147</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>144.164</t>
+          <t>108501575.458847</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3476,144 +3481,144 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>252.032</t>
+          <t>222392067.462186</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>64.683</t>
+          <t>58078615.1123888</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>71.106</t>
+          <t>63717950.2412963</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>141.808</t>
+          <t>126930634.298334</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>102.165</t>
+          <t>91908001.6040623</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>76.396</t>
+          <t>68402227.1733711</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>80.798</t>
+          <t>72485940.4665161</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>74.895</t>
+          <t>67517388.6052821</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>183.503</t>
+          <t>159399213.133763</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>75.741</t>
+          <t>68360038.5429168</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>86.205</t>
+          <t>77527350.9543626</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>63.304</t>
+          <t>57531244.6898477</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>55.338</t>
+          <t>50044861.0391757</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>52.281</t>
+          <t>47530747.951884</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>47.535</t>
+          <t>43536735.68531</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>32.504</t>
+          <t>29653705.7278062</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>27835437.547907</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>27.509</t>
+          <t>24932064.0509706</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>31.552</t>
+          <t>28520439.321036</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>13156.167</t>
+          <t>11142021264.3345</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>11233.285</t>
+          <t>9513336179.5119</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>11827.809</t>
+          <t>10017399501.4463</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>455.36</t>
+          <t>387177445.783488</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>500.182</t>
+          <t>425392701.104201</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>430.751</t>
+          <t>366356870.55283</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>458.635</t>
+          <t>390030111.999876</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>459.66</t>
+          <t>390931466.302454</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3623,144 +3628,144 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>80.058</t>
+          <t>86602712.0031154</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10.813</t>
+          <t>12746826.6600731</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>8.917</t>
+          <t>10613221.2921448</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10.107</t>
+          <t>11447600.7847715</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>63.807</t>
+          <t>68117834.9537345</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7.568</t>
+          <t>8212346.76727002</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6.111</t>
+          <t>7097049.88690405</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6.158</t>
+          <t>6642642.00062495</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>30211.98</t>
+          <t>31950549122.8739</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5.022</t>
+          <t>5894651.45210872</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>6.249</t>
+          <t>7086620.83941706</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>4.759</t>
+          <t>5602859.67157403</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>4.302</t>
+          <t>5059335.45116259</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>5.015</t>
+          <t>5900659.94366906</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4487156.14637979</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>4179520.49511903</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>129.057</t>
+          <t>136680838.330602</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>3.534</t>
+          <t>3512324.29259493</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>3.287</t>
+          <t>3487305.9410599</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2827863.31067049</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>2.849</t>
+          <t>2619349.35478367</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2752475.949391</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2.463</t>
+          <t>1873494.00525099</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2495284.03911822</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2.315</t>
+          <t>2190791.94857388</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2.529</t>
+          <t>2357360.84469069</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2.764</t>
+          <t>2632741.75028178</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3770,144 +3775,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3057.076</t>
+          <t>2704711938.70318</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.183</t>
+          <t>8516690.91166826</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8.651</t>
+          <t>8913503.82090399</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>11.362</t>
+          <t>11333020.9933979</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8.424</t>
+          <t>8843665.40360386</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6.608</t>
+          <t>6976333.84561674</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>248.822</t>
+          <t>221110787.726292</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6.637</t>
+          <t>6960344.17213837</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>5.456</t>
+          <t>5737220.66486847</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>6.658</t>
+          <t>7035491.46122318</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>6.184</t>
+          <t>6595613.73496293</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>10.166</t>
+          <t>10144439.1906972</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>5.633</t>
+          <t>5956747.89116383</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>5.731</t>
+          <t>6136315.06165209</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>5.692</t>
+          <t>6112504.40168858</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>5.134</t>
+          <t>5553772.13301866</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>5.636</t>
+          <t>6072059.33475177</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>8.398</t>
+          <t>8508176.45940566</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5532005.88968654</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>1874.653</t>
+          <t>1658200678.67472</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>1927.615</t>
+          <t>1704854198.2785</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>1983.376</t>
+          <t>1754173728.6213</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>1022.753</t>
+          <t>904846096.251853</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>985.012</t>
+          <t>871483767.682474</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>1026.673</t>
+          <t>908361933.120511</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>1055.343</t>
+          <t>933666608.020214</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>1081.823</t>
+          <t>957176218.371187</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3917,144 +3922,144 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>185.097</t>
+          <t>135582176.006572</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.206</t>
+          <t>6189700.69261733</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7.099</t>
+          <t>5305290.94334534</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6.685</t>
+          <t>4989795.49077051</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5.579</t>
+          <t>4192752.63695643</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.597</t>
+          <t>3518712.27637103</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5.094</t>
+          <t>3884005.85711672</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5.443</t>
+          <t>4145847.21116145</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5.391</t>
+          <t>4037555.81185885</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6.083</t>
+          <t>4651752.33741325</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>6.871</t>
+          <t>5243997.92547924</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>7.012</t>
+          <t>5408508.22176915</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>5.955</t>
+          <t>4417923.37330835</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6.471</t>
+          <t>4933447.99168257</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>5.665</t>
+          <t>4355247.18308277</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>5.218</t>
+          <t>4032829.66929527</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>5.275</t>
+          <t>4094109.86744255</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>4.539</t>
+          <t>3502670.53687112</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>5.419</t>
+          <t>4147521.76226445</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>119.671</t>
+          <t>86315529.1375262</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>98.528</t>
+          <t>71118227.5031188</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>106.717</t>
+          <t>76994632.3202001</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>120.976</t>
+          <t>87256250.9049141</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>120.499</t>
+          <t>86869424.1139402</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>109.647</t>
+          <t>79081404.7354449</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>116.366</t>
+          <t>83919386.0280922</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>116.302</t>
+          <t>83916961.3910207</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4064,144 +4069,144 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>51.294</t>
+          <t>46624149.1331378</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>28.315</t>
+          <t>23312742.1033055</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>29.668</t>
+          <t>24559494.191046</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>33.904</t>
+          <t>28026158.6919312</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17.231</t>
+          <t>14785226.5673917</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12.035</t>
+          <t>10430155.5705037</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12.639</t>
+          <t>10966508.5225905</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>11.041</t>
+          <t>9671202.12089258</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>11.976</t>
+          <t>10311433.5914331</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>11.532</t>
+          <t>9994608.98979532</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10.852</t>
+          <t>9322717.14374197</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>11.156</t>
+          <t>9479704.00817908</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>8.619</t>
+          <t>7302116.38387291</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>10.387</t>
+          <t>8895194.9988118</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>10.915</t>
+          <t>9364742.33179021</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>7.775</t>
+          <t>6758996.64522161</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>7012405.96666312</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>5789318.6235281</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>6379994.72466467</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>8.305</t>
+          <t>7287408.55813484</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>7.916</t>
+          <t>6920499.8685387</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>9.625</t>
+          <t>8403233.67941226</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>9.286</t>
+          <t>8067447.18790096</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>9.653</t>
+          <t>8415906.70823921</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>9.366</t>
+          <t>8192452.63143096</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>9.472</t>
+          <t>8271656.21599866</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>8.331</t>
+          <t>7295640.97736211</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4211,144 +4216,144 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>65.558</t>
+          <t>64716526.7690168</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>69.837</t>
+          <t>61716312.7527356</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>52.476</t>
+          <t>48861660.0462626</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>46.734</t>
+          <t>42432235.5664176</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2206.828</t>
+          <t>1935516899.20123</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>33.393</t>
+          <t>31462197.1914065</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>37.664</t>
+          <t>34509138.5865423</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>30745555.5847618</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>67.604</t>
+          <t>58037822.203237</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>26.413</t>
+          <t>24654964.8157788</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>20.269</t>
+          <t>18627054.8678127</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>18.068</t>
+          <t>16655432.022629</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>15.105</t>
+          <t>13673353.4403285</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>41448414.0696058</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>10481.316</t>
+          <t>9266236127.23582</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>12.615</t>
+          <t>11590304.2602387</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>13.941</t>
+          <t>12687492.1034987</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>489.172</t>
+          <t>394326016.125231</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>97.421</t>
+          <t>86441371.1933298</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>8.053</t>
+          <t>7464586.72501518</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>7.745</t>
+          <t>7200145.62356846</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>7003220.94858092</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>6.727</t>
+          <t>6241895.52695373</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>146.316</t>
+          <t>129706692.444772</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>7.665</t>
+          <t>7119353.0242439</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>7.555</t>
+          <t>7049640.26484363</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>7.356</t>
+          <t>6829764.08793309</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4358,144 +4363,144 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4300818.3329196</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23.321</t>
+          <t>19988679.3157104</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8.559</t>
+          <t>8122650.0050066</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>9.305</t>
+          <t>8699613.28311533</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>8.374</t>
+          <t>8057035.83012287</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7478792.39949166</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6.661</t>
+          <t>6464805.59980326</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>5.715</t>
+          <t>5606254.99713371</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>6.368</t>
+          <t>6128328.03127446</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>7.828</t>
+          <t>7579041.41001889</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>8.111</t>
+          <t>7858746.45735765</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>6.607</t>
+          <t>6327585.7401914</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>6.341</t>
+          <t>6002665.31801139</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>6.698</t>
+          <t>6451097.02580251</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>7.267</t>
+          <t>7028148.29614141</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>6.386</t>
+          <t>6145404.13089529</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>5.467</t>
+          <t>5368358.8816339</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>6.175</t>
+          <t>6026207.83104007</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>6.843</t>
+          <t>6647739.49358881</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>5.281</t>
+          <t>5237163.31568462</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>4.845</t>
+          <t>4816235.09495754</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>5.505</t>
+          <t>5431754.84153924</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>4.046</t>
+          <t>3962506.85640766</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4.487</t>
+          <t>4410378.48328682</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>3.793</t>
+          <t>3712804.52092396</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4021434.24310015</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>4.954</t>
+          <t>4889780.54625673</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4505,144 +4510,144 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2186.334</t>
+          <t>1763451889.84928</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>149.405</t>
+          <t>121268671.606545</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15328.666</t>
+          <t>12324115418.3076</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>81.589</t>
+          <t>68570319.621167</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>50.659</t>
+          <t>45136329.3357009</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>460.361</t>
+          <t>373621184.557314</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>35.814</t>
+          <t>31924934.6981545</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>38.272</t>
+          <t>33539910.380101</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>515.66</t>
+          <t>416434569.531223</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>30.299</t>
+          <t>26522917.5237054</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>21.072</t>
+          <t>18487010.7020676</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>155.968</t>
+          <t>126482966.147943</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>149350.56</t>
+          <t>120047884545.624</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>22.327</t>
+          <t>18756595.1757768</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>15658627.0085927</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>16.675</t>
+          <t>14283972.4474678</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>13.66</t>
+          <t>11804169.5380072</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>29.805</t>
+          <t>24743816.9957813</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>11261640.6617805</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>9767068.14201112</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>9.932</t>
+          <t>8883486.2453314</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>64.388</t>
+          <t>52459348.8277017</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>7948286.61213716</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10.275</t>
+          <t>8967379.67658149</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>11.117</t>
+          <t>9698217.74532486</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>9.819</t>
+          <t>8623123.3659952</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>10.683</t>
+          <t>9461709.9066902</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4652,144 +4657,144 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>53986456.1423477</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>57.039</t>
+          <t>43137671.0511464</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>27.741</t>
+          <t>21036989.2057965</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>30.402</t>
+          <t>23046642.439174</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23.081</t>
+          <t>17535227.1304932</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>19.132</t>
+          <t>14563715.4229728</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>16.415</t>
+          <t>12554392.3683547</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>15.611</t>
+          <t>11950833.879124</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>21.993</t>
+          <t>16735150.9896689</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>17.632</t>
+          <t>13546125.7745661</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>16.687</t>
+          <t>12806713.6065579</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>11084757.6737109</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>11469488.5031782</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>14.851</t>
+          <t>11408449.1208706</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>18.075</t>
+          <t>13843125.1148722</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>15.052</t>
+          <t>11549349.6938501</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>15.215</t>
+          <t>11690305.0335339</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>15.793</t>
+          <t>12069792.4311659</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>17.564</t>
+          <t>13386863.8482068</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>17799657.487153</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>4550966367.835</t>
+          <t>3425642730943454</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>22.464</t>
+          <t>17036868.9701863</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>-2596072592.284</t>
+          <t>-1954138195096874</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>212097.818</t>
+          <t>159652169390.215</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>202492.464</t>
+          <t>152421926980.605</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>235606.621</t>
+          <t>177347908459.034</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>246288.886</t>
+          <t>185388791394.604</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4799,144 +4804,144 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4835.751</t>
+          <t>3887976405.93678</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>66.975</t>
+          <t>54971461.9326298</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>296.171</t>
+          <t>238807718.192979</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>15.413</t>
+          <t>13138740.8782362</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>103.837</t>
+          <t>84548541.1590592</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>55.979</t>
+          <t>46217397.6583871</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>756.59</t>
+          <t>609070569.423154</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>11297947.0595468</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>95.067</t>
+          <t>77366186.6349223</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>21.328</t>
+          <t>18195644.8712618</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>16.565</t>
+          <t>14159508.1502508</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>165.564</t>
+          <t>133935564.44585</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>28.598</t>
+          <t>23662527.9881016</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>37.721</t>
+          <t>31102859.3679305</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>18.593</t>
+          <t>15915805.9322162</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>11.634</t>
+          <t>10132586.3850314</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>50.39</t>
+          <t>41134412.6025424</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>12.347</t>
+          <t>10612283.5329473</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>13.224</t>
+          <t>11477893.3971155</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>24067.022</t>
+          <t>19345382684.6165</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>7.926</t>
+          <t>6944730.02147543</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>9.542</t>
+          <t>8196880.69310461</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>10.899</t>
+          <t>9234148.8678851</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>6.175</t>
+          <t>5381626.81312451</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>7.961</t>
+          <t>6811964.48471207</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>8.563</t>
+          <t>7291643.37459945</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>6.865</t>
+          <t>6103100.54666383</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4946,144 +4951,144 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>700.425</t>
+          <t>558988202.207007</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11.342</t>
+          <t>9993498.49409731</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10483.391</t>
+          <t>8350176573.11934</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>7.253</t>
+          <t>6680691.51777019</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8.205</t>
+          <t>7589736.13606082</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>15752.8</t>
+          <t>12546904318.5381</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>419629.711</t>
+          <t>334207392249.956</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>6.228</t>
+          <t>5862404.63706147</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>5.789</t>
+          <t>5427347.86741066</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>6.222</t>
+          <t>5852247.55409869</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>18643.418</t>
+          <t>14849050510.5017</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>5.598</t>
+          <t>5250402.15540615</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>5.155</t>
+          <t>4729474.73709109</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>5.646</t>
+          <t>5314502.46251183</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4916802.15195212</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>543.011</t>
+          <t>433190021.088604</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>4.432</t>
+          <t>4176951.10800345</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>4.827</t>
+          <t>4592260.04996403</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>5.093</t>
+          <t>4830592.54871623</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>237.82</t>
+          <t>190050306.46853</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>238.539</t>
+          <t>190487112.770428</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>237.944</t>
+          <t>190091458.65707</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>13.244</t>
+          <t>11047970.1517367</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13.183</t>
+          <t>11032709.0982941</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>12.985</t>
+          <t>10843528.3557134</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13.279</t>
+          <t>11104388.9370067</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>13.276</t>
+          <t>11164678.9587901</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,144 +5098,144 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>63.812</t>
+          <t>51416208.4080463</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>45.641</t>
+          <t>38231717.4117131</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35.369</t>
+          <t>29106706.9059667</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>32.014</t>
+          <t>26393401.9449976</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>32.839</t>
+          <t>27210545.9805003</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>28.939</t>
+          <t>24688503.3841615</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>28.556</t>
+          <t>24024668.9230061</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>25.977</t>
+          <t>22229993.5333774</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>26.482</t>
+          <t>22673409.1681916</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>24.522</t>
+          <t>20922613.1499958</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>20.217</t>
+          <t>17204080.8976802</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>48.638</t>
+          <t>39874800.5605102</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>14.465</t>
+          <t>12233963.3737644</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>13.357</t>
+          <t>11519885.3642951</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>14.272</t>
+          <t>12250311.2775477</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>12.255</t>
+          <t>10547263.5945846</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>12.379</t>
+          <t>10815343.3999931</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>11.793</t>
+          <t>10314570.4975906</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>11.491</t>
+          <t>10016762.4524012</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>14.552</t>
+          <t>12618778.1952266</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>14.768</t>
+          <t>12780123.4088473</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>14.521</t>
+          <t>12660343.5076455</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>12.426</t>
+          <t>10724730.2151201</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14.405</t>
+          <t>12461111.3012392</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>13.261</t>
+          <t>11477161.6886509</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13.685</t>
+          <t>11837261.3910351</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>13.998</t>
+          <t>12137912.2622425</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5240,144 +5245,144 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>16.591</t>
+          <t>13287249.5614817</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>12191061.4303064</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13.043</t>
+          <t>10165570.8595657</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>12.739</t>
+          <t>9907090.43453689</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>13.966</t>
+          <t>10774942.3481217</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>13.462</t>
+          <t>10558545.357219</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>10041337.7997388</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>12.556</t>
+          <t>9788998.23629321</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>12.063</t>
+          <t>9384118.59922632</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>18.126</t>
+          <t>13810398.9246758</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>10.317</t>
+          <t>8134818.46821435</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>10.391</t>
+          <t>8091917.19718034</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>51692.296</t>
+          <t>37718309973.1579</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>9.445</t>
+          <t>7477486.93567099</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>9.393</t>
+          <t>7324500.52934837</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>8.929</t>
+          <t>6958552.77036201</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>6681025.56064037</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>8.467</t>
+          <t>6692546.55458014</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>8.397</t>
+          <t>6686153.82686696</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>7.169</t>
+          <t>5659769.69120866</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>6.795</t>
+          <t>5337572.64267709</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>6.628</t>
+          <t>5211650.49786752</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>5067892.88120639</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>6.546</t>
+          <t>5137584.74726347</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>6.325</t>
+          <t>4973141.96777206</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>6.275</t>
+          <t>4948094.35046241</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>5148040.93783187</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5387,144 +5392,144 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>243.824</t>
+          <t>167671875.897439</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>418.855</t>
+          <t>303661904.892517</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>69.653</t>
+          <t>49968733.7782011</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>95.581</t>
+          <t>68287325.3178587</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>107.966</t>
+          <t>77275720.6097502</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>230.689</t>
+          <t>167225204.487007</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>70.527</t>
+          <t>50818922.8336711</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>56.781</t>
+          <t>40945555.0615343</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>52.353</t>
+          <t>37779929.4507758</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>42.887</t>
+          <t>31210618.0315869</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>37.013</t>
+          <t>27051753.8725476</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>27.537</t>
+          <t>20155372.200757</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>22.837</t>
+          <t>16654681.6951238</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>26.352</t>
+          <t>18978724.0164919</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>18.962</t>
+          <t>13797331.6753668</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>18.989</t>
+          <t>13917785.8996051</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>18.913</t>
+          <t>13873194.3610255</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>18.728</t>
+          <t>13697260.6052546</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>16.277</t>
+          <t>11944677.4041858</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>494.193</t>
+          <t>360432540.354758</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>456.924</t>
+          <t>333293249.638308</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>499.87</t>
+          <t>364596774.727035</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>431.143</t>
+          <t>314390686.427555</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>478.485</t>
+          <t>349027043.455203</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>451.636</t>
+          <t>329430495.833413</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>485.021</t>
+          <t>353794164.813589</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>480.235</t>
+          <t>350316028.295831</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5534,144 +5539,144 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>164.135</t>
+          <t>149170103.394264</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>40.181</t>
+          <t>35869705.968947</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>38.245</t>
+          <t>35634046.0553828</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>51.672</t>
+          <t>47313780.6347884</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>61.288</t>
+          <t>56979430.0045545</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>47.525</t>
+          <t>43572761.4344714</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>41.246</t>
+          <t>37661143.4957597</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>36.916</t>
+          <t>33576080.7521703</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>36.581</t>
+          <t>33632144.3488023</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>30.785</t>
+          <t>28064955.5938021</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>24.242</t>
+          <t>22242804.7966864</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>18.275</t>
+          <t>16714082.4299125</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>14.822</t>
+          <t>13445619.2714641</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>13.895</t>
+          <t>12844239.7480085</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>15486606.4960799</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>11.474</t>
+          <t>10622812.5990147</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>11.952</t>
+          <t>11169932.0993751</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>8.866</t>
+          <t>8267621.95641382</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>9.607</t>
+          <t>8952300.44172704</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>27.575</t>
+          <t>24266162.7570739</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>29.205</t>
+          <t>25686200.097905</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26.993</t>
+          <t>23716272.9833902</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>25.334</t>
+          <t>22355451.7257493</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>25.755</t>
+          <t>22738160.5880976</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>22.609</t>
+          <t>20007798.872771</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>27.087</t>
+          <t>24034292.020685</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>32.758</t>
+          <t>29138719.2102243</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5681,144 +5686,144 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>504.006</t>
+          <t>366968292.594568</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>520.16</t>
+          <t>372934834.017617</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>562.234</t>
+          <t>404402002.988532</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>407.893</t>
+          <t>293012830.385418</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>329.837</t>
+          <t>237133749.533776</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>95.881</t>
+          <t>69508642.1963751</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>330.27</t>
+          <t>237607446.128822</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>251.201</t>
+          <t>180757601.849001</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>63.242</t>
+          <t>45950753.4690675</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>69.497</t>
+          <t>50517942.6929715</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>369.165</t>
+          <t>265293186.248899</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>108.623</t>
+          <t>78350229.0167827</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>3276.001</t>
+          <t>2349161788.01491</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>44.886</t>
+          <t>32751413.8014672</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>73.907</t>
+          <t>53475750.0032452</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>54.816</t>
+          <t>39715021.6339071</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>59.478</t>
+          <t>43165094.6268412</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>64.488</t>
+          <t>46730950.0261177</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>65.266</t>
+          <t>47363914.2887824</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>60.515</t>
+          <t>43709820.6285791</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>42.51</t>
+          <t>30767931.8900268</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>50.283</t>
+          <t>36425745.2493165</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>39.939</t>
+          <t>28975068.9135118</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>44.993</t>
+          <t>32575105.9537996</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>42.641</t>
+          <t>30865804.3940928</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>38.768</t>
+          <t>28140277.8853752</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>26.374</t>
+          <t>19206133.1675748</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5828,144 +5833,144 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>28.384</t>
+          <t>21128434.8784141</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>21.459</t>
+          <t>16720713.4762495</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18.076</t>
+          <t>13630578.1710289</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>26.271</t>
+          <t>19226604.3421963</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>15.016</t>
+          <t>11283285.8305409</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>10551783.4081635</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>15585778.371958</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>15.586</t>
+          <t>11505739.5028496</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>13.714</t>
+          <t>10065541.9688229</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>13.215</t>
+          <t>9756554.87361148</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>13.029</t>
+          <t>9652471.54589023</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>12.576</t>
+          <t>9581534.64372102</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>12.364</t>
+          <t>9041835.3902223</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>24176.323</t>
+          <t>16438083721.3653</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>11.329</t>
+          <t>8257244.62477351</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>56.635</t>
+          <t>39087940.0126098</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>77696.81</t>
+          <t>55586817859.9794</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>9.633</t>
+          <t>7177753.50244561</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>7.522</t>
+          <t>5663555.80077387</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2267.287</t>
+          <t>1612803897.7477</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>2314.609</t>
+          <t>1646353696.03114</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>3668206.035</t>
+          <t>2616867466713.89</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>156.138</t>
+          <t>107186433.626755</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>2611.512</t>
+          <t>1863842785.96276</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2696.141</t>
+          <t>1924208245.50973</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2889.418</t>
+          <t>2062306400.11405</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>2995.223</t>
+          <t>2137865251.43259</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5975,144 +5980,144 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>356.776</t>
+          <t>243621742.902258</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>29403431.004</t>
+          <t>19991454508738.9</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6.327</t>
+          <t>4611670.37539351</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7.442</t>
+          <t>5399492.13661448</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1289.109</t>
+          <t>876829145.967606</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5.617</t>
+          <t>4150755.50449242</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>4362518.16643208</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>426.802</t>
+          <t>290519764.043073</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>5.182</t>
+          <t>3807827.95848382</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>888.091</t>
+          <t>604164373.682605</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>4.561</t>
+          <t>3449196.86159492</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1216.108</t>
+          <t>827354663.128819</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>4.351</t>
+          <t>3207020.97516109</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>4.363</t>
+          <t>3282522.89718737</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>3671447.82332148</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>3.573</t>
+          <t>2692743.55757112</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>3.488</t>
+          <t>2681308.42556357</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>2607754.89107665</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>3.436</t>
+          <t>2624248.01729781</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>3.441</t>
+          <t>2615502.3617215</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>3.315</t>
+          <t>2512455.29218814</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2.915</t>
+          <t>2211136.51551994</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2383370.53688255</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>2.595</t>
+          <t>1957811.77925711</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2.399</t>
+          <t>1792220.73597953</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2.556</t>
+          <t>1924437.89540058</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>2.789</t>
+          <t>2117232.01808648</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6122,144 +6127,144 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>73.706</t>
+          <t>72647411.7159474</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>26.367</t>
+          <t>27523428.4965108</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>23.042</t>
+          <t>23471973.816631</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>23.054</t>
+          <t>23692258.0704974</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>23.991</t>
+          <t>25762375.998628</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>18557402.3716151</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>24481571.9591253</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>21.704</t>
+          <t>23053265.3519649</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>20.187</t>
+          <t>21243437.75434</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>16.399</t>
+          <t>17810557.1979092</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>15.379</t>
+          <t>16340039.5699578</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>14.789</t>
+          <t>15807366.4553753</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>11.242</t>
+          <t>11669117.329031</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>10.893</t>
+          <t>11768294.5604643</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>12.449</t>
+          <t>12836875.4842316</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>8.375</t>
+          <t>8607419.18865432</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>10.626</t>
+          <t>11039806.7057442</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>9.766</t>
+          <t>10325660.3329777</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>9.604</t>
+          <t>9817984.2687775</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>15.092</t>
+          <t>15255337.8165813</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>12.545</t>
+          <t>12654076.0728858</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>14.213</t>
+          <t>14256153.1299599</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>14.818</t>
+          <t>14877480.095279</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14.538</t>
+          <t>14626081.2266027</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>12.911</t>
+          <t>12826162.1559568</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13.631</t>
+          <t>13760549.3362098</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>12.283</t>
+          <t>12320268.3596866</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6269,144 +6274,144 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>39.641</t>
+          <t>45631964.9436493</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>17.934</t>
+          <t>19276281.4316062</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>18.17</t>
+          <t>19292912.1635728</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>15.735</t>
+          <t>16854685.3371351</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>15.135</t>
+          <t>16393878.3923213</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>12.501</t>
+          <t>13507308.1906608</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>13.573</t>
+          <t>14719681.3213898</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>14.492</t>
+          <t>15957773.203811</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>17967730.5024808</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>18.185</t>
+          <t>20091279.761967</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>15.965</t>
+          <t>18325944.1150734</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>16349144.695494</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>12.603</t>
+          <t>13776546.7613746</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>13.682</t>
+          <t>15415563.2596341</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>16967237.6893515</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>12.226</t>
+          <t>13674254.8769271</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>12.372</t>
+          <t>15424811.4015414</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>10.764</t>
+          <t>11921359.9927996</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>11.454</t>
+          <t>12762248.895663</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>14.931</t>
+          <t>12175772.3965051</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>11.622</t>
+          <t>11201050.5313553</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>13.559</t>
+          <t>15618945.0123119</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>13.206</t>
+          <t>10380811.5230839</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10.413</t>
+          <t>11672138.194238</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>9.529</t>
+          <t>10656529.7097281</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>9.548</t>
+          <t>10673140.0362287</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>16.845</t>
+          <t>16202343.3092179</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6416,144 +6421,144 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>15.142</t>
+          <t>11776327.6933601</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4.079</t>
+          <t>3252843.30559764</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.674</t>
+          <t>2942925.82576691</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3.396</t>
+          <t>2706584.46299524</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3.485</t>
+          <t>2828252.2091915</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.198</t>
+          <t>2593062.07596059</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2.747</t>
+          <t>2240342.0093396</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.974</t>
+          <t>2431023.63215106</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>3.363</t>
+          <t>2738671.07389969</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2508832.85668101</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>3.082</t>
+          <t>2519445.81134649</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2.814</t>
+          <t>2309280.51440803</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2.659</t>
+          <t>2145551.59357635</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2.964</t>
+          <t>2416428.5839186</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2.885</t>
+          <t>2342016.27473151</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2.389</t>
+          <t>1957404.70867194</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2.552</t>
+          <t>2103992.64146729</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2.194</t>
+          <t>1804359.90151406</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2.186</t>
+          <t>1785368.18789208</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>6.294</t>
+          <t>4855054.22202052</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>5.143</t>
+          <t>3964912.41660826</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>6.996</t>
+          <t>5368344.59049228</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>4582004.31502265</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>6.932</t>
+          <t>5324335.10156113</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>7.325</t>
+          <t>5603613.2900475</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>5.411</t>
+          <t>4169558.71245632</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>7.903</t>
+          <t>6065599.18299962</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6565,7 +6570,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6575,144 +6580,144 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>22634988.814</t>
+          <t>19286691579283.2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>30953695.241</t>
+          <t>21303347066604.5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>28555.158</t>
+          <t>23026160767.6195</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>5053.451</t>
+          <t>4464631426.8718</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>5934.263</t>
+          <t>4973797625.91927</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>20730.492</t>
+          <t>17556602773.4903</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>422862.899</t>
+          <t>337011496903.692</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2174.67</t>
+          <t>1845477251.30151</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>32538.436</t>
+          <t>33987831212.1455</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2446.52</t>
+          <t>2025473627.52797</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>30051.795</t>
+          <t>25009416219.9205</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>3329.483</t>
+          <t>2645107417.38288</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>205397.018</t>
+          <t>161105284994.992</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>68854.518</t>
+          <t>54313408054.9366</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>13088.001</t>
+          <t>11968206663.6603</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1453.02</t>
+          <t>1260596440.43779</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>78676.915</t>
+          <t>56505930384.0673</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1266.077</t>
+          <t>1105838478.78276</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>849.286</t>
+          <t>776363999.064357</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>40149978.512</t>
+          <t>36058117345859.2</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>4553651202.698</t>
+          <t>3427991302318225</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>10246478.839</t>
+          <t>8360187339234.57</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>-2590669942.005</t>
+          <t>-1949465785401533</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3493029.498</t>
+          <t>3018096900045.83</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>3274108.926</t>
+          <t>2830107480276.86</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>3561627.885</t>
+          <t>3072019336139.58</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>3647297.304</t>
+          <t>3142586218067.49</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6722,144 +6727,144 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>96.571</t>
+          <t>121928205.745403</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>229.281</t>
+          <t>263177640.514517</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>28.294</t>
+          <t>39088603.787012</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>26.215</t>
+          <t>36813547.2872088</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>24.076</t>
+          <t>33389475.0654976</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2657.649</t>
+          <t>2973582423.06383</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>30154655.9206691</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>22.232</t>
+          <t>30556879.2895058</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>21.043</t>
+          <t>28895411.9919259</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>26224444.9449791</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1390.233</t>
+          <t>1556724897.91402</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>23.304</t>
+          <t>33718753.883431</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>14.956</t>
+          <t>20747027.638598</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>16.384</t>
+          <t>22672799.238522</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>20944633.3206855</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>14.823</t>
+          <t>21298503.2771584</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>14.515</t>
+          <t>20458404.2133657</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>13.718</t>
+          <t>19177809.3768537</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>16.147</t>
+          <t>21817794.6916169</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>92.809</t>
+          <t>107627474.161406</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>90.774</t>
+          <t>105029766.292524</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>89.787</t>
+          <t>104219069.032898</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>39.736</t>
+          <t>49543840.1101356</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>49.812</t>
+          <t>61910540.2766158</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>54399930.0288436</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>51115042.9672657</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>40.521</t>
+          <t>49002720.7752324</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6869,144 +6874,144 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>7.616</t>
+          <t>8728185.67727595</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5.247</t>
+          <t>5678480.47395134</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>4.977</t>
+          <t>5427958.46123227</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>5.434</t>
+          <t>5904396.93967008</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>5.101</t>
+          <t>5631572.07050566</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5.108</t>
+          <t>5619207.79295886</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5.126</t>
+          <t>5689240.604429</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>5.278</t>
+          <t>5744886.01409631</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>4.946</t>
+          <t>5472343.93755942</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>5.204</t>
+          <t>5788527.16164776</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>4.607</t>
+          <t>5178577.64777137</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>4.464</t>
+          <t>4993529.81949</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>4.519</t>
+          <t>4944035.91690747</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>4.914</t>
+          <t>5463768.00197719</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>4571651.7654436</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>3.273</t>
+          <t>3607989.42192166</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>3.137</t>
+          <t>3542209.09384045</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>3.121</t>
+          <t>3474120.95475605</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>3.304</t>
+          <t>3647566.34529426</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>34973798.414</t>
+          <t>31596168691609.4</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2777635.41362391</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2.559</t>
+          <t>2880498.24729895</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2.556</t>
+          <t>2829129.24724367</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>2.919</t>
+          <t>3265496.17569477</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2.412</t>
+          <t>2703958.03639771</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2.564</t>
+          <t>2882393.772792</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>2.977</t>
+          <t>3488176.28531473</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7016,144 +7021,144 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>6.903</t>
+          <t>6973372.99910857</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>30.023</t>
+          <t>27387781.9880504</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5.786</t>
+          <t>5760789.136716</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>5.968</t>
+          <t>5929179.24748867</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>5.648</t>
+          <t>5640956.97764137</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.623</t>
+          <t>4596440.18637828</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5.373</t>
+          <t>5215441.43650847</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>4.261</t>
+          <t>4250969.55987076</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>4.141</t>
+          <t>4195050.12272614</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>4.446</t>
+          <t>4437070.48451898</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>3.658</t>
+          <t>3695634.96143049</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>3.107</t>
+          <t>3145309.4871415</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>3.496</t>
+          <t>3473823.42599664</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>42667.271</t>
+          <t>36128705455.0051</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>3.137</t>
+          <t>3210584.31887837</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2.628</t>
+          <t>2720827.62071738</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2.754</t>
+          <t>2875630.02927664</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>4.108</t>
+          <t>4215987.58083065</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>4.499</t>
+          <t>4813032.09975445</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>3.346</t>
+          <t>3505290.75750447</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3490695.80029453</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>3.303</t>
+          <t>3359985.83036539</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2.876</t>
+          <t>2921691.75869538</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>2.851</t>
+          <t>2877035.92657833</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>3.026</t>
+          <t>3041428.64084542</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2.961</t>
+          <t>3012283.79924241</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>3.149</t>
+          <t>3187011.00420639</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7163,144 +7168,144 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>24.337</t>
+          <t>23012583.2398939</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1532826.247</t>
+          <t>1297907463742.3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>26.874</t>
+          <t>24794581.2231271</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>30.751</t>
+          <t>28522555.1712021</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>26.643</t>
+          <t>24747448.6064336</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>22.632</t>
+          <t>21340866.2969492</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>21.359</t>
+          <t>20032729.8881551</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>17758727.3966184</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>18.291</t>
+          <t>17276052.4482042</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15221749.9140243</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>12.589</t>
+          <t>12151533.5834368</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>11.638</t>
+          <t>11294034.3669472</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>11.683</t>
+          <t>11038848.787434</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>13.104</t>
+          <t>12575788.9887211</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>10.637</t>
+          <t>10381568.0437323</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>7.975</t>
+          <t>7758654.93281257</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>7130591.84649781</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>7.473</t>
+          <t>7346321.94887569</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>8.41</t>
+          <t>8182760.25671536</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>9.569</t>
+          <t>9199963.6861743</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>7198317.66458086</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>8.556</t>
+          <t>8146299.83302644</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>7.777</t>
+          <t>7464413.12890227</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>8.179</t>
+          <t>7760015.57609369</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>8.659</t>
+          <t>8168618.7927194</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>8.134</t>
+          <t>7761817.90111668</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>8.232</t>
+          <t>7851575.26780871</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7310,144 +7315,144 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2969065.076</t>
+          <t>2652177000377.21</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>94.798</t>
+          <t>93373883.5932273</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>89.63</t>
+          <t>88523942.1313307</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>101.075</t>
+          <t>99895951.0818809</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>116.606</t>
+          <t>114404977.949716</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>96.31</t>
+          <t>95209289.0557627</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>98.986</t>
+          <t>97603304.2884161</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>104.451</t>
+          <t>102707826.879962</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>116.126</t>
+          <t>115785463.047151</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>106.443</t>
+          <t>105126702.189768</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>101.359</t>
+          <t>99720733.2683493</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>96.497</t>
+          <t>95026711.8347853</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>87.776</t>
+          <t>86176164.469446</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>94.846</t>
+          <t>92723127.6775709</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>86.211</t>
+          <t>84672724.0485234</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>68.559</t>
+          <t>67155512.5613336</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>65.191</t>
+          <t>63363263.2718377</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>57.334</t>
+          <t>55988707.3298112</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>57.044</t>
+          <t>55720377.6133612</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>699345.864</t>
+          <t>624700925828.909</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>542702.041</t>
+          <t>484777665320.777</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>609101.493</t>
+          <t>544088890605.127</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>577858.789</t>
+          <t>516181254234.533</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>589448.514</t>
+          <t>526533679520.195</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>512854.611</t>
+          <t>458115339511.216</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>539473.965</t>
+          <t>481892862870.33</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>520891.494</t>
+          <t>465294582237.605</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,144 +7462,144 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1062.434</t>
+          <t>953414323.958279</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>32.382</t>
+          <t>31430108.0194969</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>28.119</t>
+          <t>27307800.8642268</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>28.842</t>
+          <t>28153005.8773951</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>29.819</t>
+          <t>29095432.3743452</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>23.248</t>
+          <t>22723250.1906698</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>24.332</t>
+          <t>23799137.6647039</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>30.509</t>
+          <t>29888623.5260063</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>34.879</t>
+          <t>34088145.5224151</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>32.595</t>
+          <t>31882038.782365</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>27.647</t>
+          <t>26886498.1801147</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>23.837</t>
+          <t>23223834.614366</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>22.808</t>
+          <t>22233911.6867418</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>23.031</t>
+          <t>22477750.3627382</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>23.944</t>
+          <t>23409881.1789789</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>18.952</t>
+          <t>18430512.6827815</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>18.453</t>
+          <t>17982193.9602953</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>16175086.8142816</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>16.158</t>
+          <t>15775691.6016665</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>287.664</t>
+          <t>258057253.586484</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>303.75</t>
+          <t>272214342.100583</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>239.933</t>
+          <t>215449929.854947</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>234.258</t>
+          <t>210259979.790091</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>257.358</t>
+          <t>230959673.594121</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>251.164</t>
+          <t>225337253.689444</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>248.825</t>
+          <t>223296402.693668</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>246.717</t>
+          <t>221373153.819607</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7604,144 +7609,144 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>222739.445</t>
+          <t>195099566760.114</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>313.455</t>
+          <t>328771456.247104</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>278.279</t>
+          <t>290597927.706675</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>295.521</t>
+          <t>304170982.148922</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>362.413</t>
+          <t>371753371.859676</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>319.235</t>
+          <t>329443412.325867</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>273.165</t>
+          <t>279709783.562437</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>251.241</t>
+          <t>254274470.183517</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>247.347</t>
+          <t>250699607.570325</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>238.069</t>
+          <t>241806942.58987</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2905.603</t>
+          <t>2570656047.79548</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>157.92</t>
+          <t>160037970.162459</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>145.749</t>
+          <t>148802753.802091</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>113.692</t>
+          <t>115301157.104113</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>143.008</t>
+          <t>144395250.777062</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>141.52</t>
+          <t>141938852.783892</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>114.014</t>
+          <t>114513726.407719</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>108.195</t>
+          <t>108757858.650422</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>97.43</t>
+          <t>98027487.1211027</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>27136.753</t>
+          <t>23775617545.08</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>28337.779</t>
+          <t>24825243936.5357</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>3405755.888</t>
+          <t>2981766589089.27</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>23617.742</t>
+          <t>20689489437.4865</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>26436.225</t>
+          <t>23157360589.3219</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>26799.233</t>
+          <t>23475121357.1311</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>30211.663</t>
+          <t>26464147441.2082</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>31351.978</t>
+          <t>27460886830.7074</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7751,144 +7756,144 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>14790220.152</t>
+          <t>12505512580898.2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>204.263</t>
+          <t>197900823.340385</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>174.66</t>
+          <t>169994217.761405</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>175.431</t>
+          <t>170964556.434051</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>174.107</t>
+          <t>170128329.804036</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>157.896</t>
+          <t>154154343.586094</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>148.951</t>
+          <t>145988450.673565</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>143.365</t>
+          <t>139776968.501832</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>154.359</t>
+          <t>150083009.900591</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>149.186</t>
+          <t>145543307.947375</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>5350.221</t>
+          <t>4540863578.33815</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>114.147</t>
+          <t>111565479.285598</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>108.178</t>
+          <t>104795084.998361</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>107.948</t>
+          <t>105121671.38702</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>112.564</t>
+          <t>108838651.726881</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>88.942</t>
+          <t>86649043.2064511</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>94.54</t>
+          <t>92197032.5082085</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>77.722</t>
+          <t>76179550.5166438</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>76.197</t>
+          <t>73665282.0689146</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>3656454.949</t>
+          <t>3091623799597.22</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>1441197.054</t>
+          <t>1218571684207.83</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>1761877.828</t>
+          <t>1489715456571.59</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>3569401.952</t>
+          <t>3018017729996.54</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>1898075.374</t>
+          <t>1604872562325.72</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>1836851.776</t>
+          <t>1553106375862.73</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2004569.992</t>
+          <t>1694916477843.62</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>2098539.659</t>
+          <t>1774369953689.43</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7898,137 +7903,137 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>4627966.884</t>
+          <t>3913055225827.23</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>12.364</t>
+          <t>11329019.6412354</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>11.413</t>
+          <t>10626235.7567354</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>12.047</t>
+          <t>11166768.2926749</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>11.901</t>
+          <t>11232246.7020378</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>9.415</t>
+          <t>8945115.06476258</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>9.702</t>
+          <t>9337321.89041161</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>10.888</t>
+          <t>10323423.1771099</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11219312.1796562</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>12.959</t>
+          <t>12257824.8313415</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>11.134</t>
+          <t>10485083.9362408</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>11.489</t>
+          <t>10862659.2034018</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>11.137</t>
+          <t>10363195.1433072</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>11.484</t>
+          <t>10726845.9970379</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>11.875</t>
+          <t>11119382.8117938</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>9.038</t>
+          <t>8521419.58457973</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>8.139</t>
+          <t>7680783.92713408</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>8.303</t>
+          <t>7832324.05498445</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>8.036</t>
+          <t>7599133.24824</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>514327.289</t>
+          <t>434876279872.915</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>426739.672</t>
+          <t>360818839759.062</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>512208.017</t>
+          <t>433084253965.909</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>521603.511</t>
+          <t>441028335418.145</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>526227.751</t>
+          <t>444938233901.19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>455027.441</t>
+          <t>384736657097.922</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>509119.037</t>
+          <t>430472407206.996</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>507651.229</t>
+          <t>429231362443.2</t>
         </is>
       </c>
     </row>
@@ -8070,6 +8075,11 @@
           <t>value.m.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8104,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
